--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1646,22 +1646,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.9%</t>
         </is>
       </c>
     </row>
@@ -1728,22 +1728,22 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>77.2%</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -8740,45 +8740,49 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C176" s="5" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E176" s="5" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G176" s="5" t="inlineStr"/>
-      <c r="H176" s="5" t="inlineStr">
-        <is>
-          <t>0/50</t>
-        </is>
-      </c>
-      <c r="I176" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Mona Hazaa</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>48/50</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10532,45 +10536,49 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
+      <c r="C216" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D216" s="5" t="inlineStr">
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E216" s="5" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr"/>
-      <c r="H216" s="5" t="inlineStr">
-        <is>
-          <t>0/47</t>
-        </is>
-      </c>
-      <c r="I216" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Mona Hazaa</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>42/47</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13518,7 +13526,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -15326,7 +15334,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.4%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1334,22 +1334,22 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>18</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.8%</t>
         </is>
       </c>
     </row>
@@ -2618,45 +2618,49 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Tasneem El-Sayed</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>40/42</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3425,7 +3429,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1806,22 +1806,22 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -1884,22 +1884,22 @@
         <v>40</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -12845,45 +12845,49 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C267" s="5" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E267" s="5" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G267" s="5" t="inlineStr"/>
-      <c r="H267" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I267" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Amir, Git Department D Bassant</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13534,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13718,7 +13722,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14653,45 +14657,49 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B307" s="5" t="inlineStr">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C307" s="5" t="inlineStr">
+      <c r="C307" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D307" s="5" t="inlineStr">
+      <c r="D307" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E307" s="5" t="inlineStr">
+      <c r="E307" s="2" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="F307" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G307" s="5" t="inlineStr"/>
-      <c r="H307" s="5" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I307" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Amir, Git Department D Bassant</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>28/36</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15346,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15526,7 +15534,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1337,10 +1337,10 @@
         <v>15</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>19</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         <v>18</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         <v>10</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         <v>20</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
         <v>18</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         <v>23</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         <v>23</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2708,45 +2708,45 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4117,45 +4117,45 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr"/>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6104,45 +6104,45 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr">
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8165,45 +8165,45 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr">
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I163" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8842,45 +8842,45 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G178" s="6" t="inlineStr"/>
-      <c r="H178" s="6" t="inlineStr">
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr"/>
+      <c r="H178" s="5" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I178" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10642,45 +10642,45 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
+      <c r="C218" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D218" s="6" t="inlineStr">
+      <c r="D218" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F218" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G218" s="6" t="inlineStr"/>
-      <c r="H218" s="6" t="inlineStr">
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr"/>
+      <c r="H218" s="5" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I218" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I218" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12904,45 +12904,45 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D268" s="6" t="inlineStr">
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="6" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr"/>
+      <c r="H268" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I268" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I268" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14716,45 +14716,45 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B308" s="6" t="inlineStr">
+      <c r="A308" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B308" s="5" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C308" s="6" t="inlineStr">
+      <c r="C308" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D308" s="6" t="inlineStr">
+      <c r="D308" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="E308" s="5" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F308" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G308" s="6" t="inlineStr"/>
-      <c r="H308" s="6" t="inlineStr">
+      <c r="F308" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G308" s="5" t="inlineStr"/>
+      <c r="H308" s="5" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I308" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I308" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
@@ -1490,22 +1490,22 @@
         <v>47</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>23</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -1806,22 +1806,22 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>16</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -1884,22 +1884,22 @@
         <v>40</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>16</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>80.9%</t>
         </is>
       </c>
     </row>
@@ -6104,45 +6104,49 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr"/>
-      <c r="H116" s="5" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Yousra Saleh</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>43/43</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12893,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -12904,45 +12908,49 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B268" s="5" t="inlineStr">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C268" s="5" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E268" s="5" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G268" s="5" t="inlineStr"/>
-      <c r="H268" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I268" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Git Department D Bassant, Yousra</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>28/28</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13499,7 +13507,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13546,7 +13554,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13781,7 +13789,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14701,7 +14709,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14716,45 +14724,49 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B308" s="5" t="inlineStr">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C308" s="5" t="inlineStr">
+      <c r="C308" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D308" s="5" t="inlineStr">
+      <c r="D308" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E308" s="5" t="inlineStr">
+      <c r="E308" s="2" t="inlineStr">
         <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="F308" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G308" s="5" t="inlineStr"/>
-      <c r="H308" s="5" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I308" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>Git Department D Bassant, Yousra</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>33/36</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15323,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15358,7 +15370,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15593,7 +15605,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9">
@@ -1337,10 +1337,10 @@
         <v>16</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         <v>20</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1493,10 +1493,10 @@
         <v>19</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         <v>11</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         <v>21</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
         <v>19</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         <v>24</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         <v>24</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2755,45 +2755,45 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4168,45 +4168,45 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6159,45 +6159,45 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C117" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="E117" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr"/>
-      <c r="H117" s="6" t="inlineStr">
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr"/>
+      <c r="H117" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6589,45 +6589,45 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8396,45 +8396,45 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G168" s="6" t="inlineStr"/>
-      <c r="H168" s="6" t="inlineStr">
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr"/>
+      <c r="H168" s="5" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8905,45 +8905,45 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C179" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E179" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G179" s="6" t="inlineStr"/>
-      <c r="H179" s="6" t="inlineStr">
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr"/>
+      <c r="H179" s="5" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I179" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10709,45 +10709,45 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B219" s="6" t="inlineStr">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
+      <c r="C219" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D219" s="6" t="inlineStr">
+      <c r="D219" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G219" s="6" t="inlineStr"/>
-      <c r="H219" s="6" t="inlineStr">
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr"/>
+      <c r="H219" s="5" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I219" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I219" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12975,45 +12975,45 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
+      <c r="C269" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D269" s="6" t="inlineStr">
+      <c r="D269" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="6" t="inlineStr">
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr"/>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I269" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I269" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -14791,45 +14791,45 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B309" s="6" t="inlineStr">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B309" s="5" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C309" s="6" t="inlineStr">
+      <c r="C309" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D309" s="6" t="inlineStr">
+      <c r="D309" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="E309" s="5" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="F309" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G309" s="6" t="inlineStr"/>
-      <c r="H309" s="6" t="inlineStr">
+      <c r="F309" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G309" s="5" t="inlineStr"/>
+      <c r="H309" s="5" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I309" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I309" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -12949,7 +12949,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -12949,7 +12949,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>82.3%</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1818,22 +1818,22 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
     </row>
@@ -1896,22 +1896,22 @@
         <v>40</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>14</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -13058,45 +13058,49 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C270" s="5" t="inlineStr">
+      <c r="C270" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E270" s="5" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G270" s="5" t="inlineStr"/>
-      <c r="H270" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I270" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>Git Department D Bassant</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>26/28</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13571,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13849,7 +13853,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14878,45 +14882,49 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B310" s="5" t="inlineStr">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C310" s="5" t="inlineStr">
+      <c r="C310" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D310" s="5" t="inlineStr">
+      <c r="D310" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E310" s="5" t="inlineStr">
+      <c r="E310" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F310" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G310" s="5" t="inlineStr"/>
-      <c r="H310" s="5" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I310" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Git Department D Bassant</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>27/36</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15395,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15669,7 +15677,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
         <v>47</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
@@ -6226,45 +6226,49 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr"/>
-      <c r="H118" s="5" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Yousra Saleh</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>35/43</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13587,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13630,7 +13634,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13865,7 +13869,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15407,7 +15411,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15454,7 +15458,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15689,7 +15693,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15650,7 +15650,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1345,10 +1345,10 @@
         <v>21</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>22</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>21</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>12</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         <v>23</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         <v>21</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         <v>26</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>26</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -1920,45 +1920,45 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4712,45 +4712,45 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6277,45 +6277,45 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr"/>
-      <c r="H119" s="6" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr"/>
+      <c r="H119" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8303,45 +8303,45 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C165" s="6" t="inlineStr">
+      <c r="C165" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D165" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G165" s="6" t="inlineStr"/>
-      <c r="H165" s="6" t="inlineStr">
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr"/>
+      <c r="H165" s="5" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9039,45 +9039,45 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
+      <c r="C181" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G181" s="6" t="inlineStr"/>
-      <c r="H181" s="6" t="inlineStr">
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr"/>
+      <c r="H181" s="5" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10851,45 +10851,45 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C221" s="6" t="inlineStr">
+      <c r="C221" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D221" s="6" t="inlineStr">
+      <c r="D221" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="E221" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G221" s="6" t="inlineStr"/>
-      <c r="H221" s="6" t="inlineStr">
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="inlineStr"/>
+      <c r="H221" s="5" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I221" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I221" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13125,45 +13125,45 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
+      <c r="C271" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D271" s="6" t="inlineStr">
+      <c r="D271" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="6" t="inlineStr">
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr"/>
+      <c r="H271" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I271" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I271" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -14949,45 +14949,45 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B311" s="6" t="inlineStr">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C311" s="6" t="inlineStr">
+      <c r="C311" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D311" s="6" t="inlineStr">
+      <c r="D311" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="E311" s="5" t="inlineStr">
         <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="F311" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G311" s="6" t="inlineStr"/>
-      <c r="H311" s="6" t="inlineStr">
+      <c r="F311" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G311" s="5" t="inlineStr"/>
+      <c r="H311" s="5" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I311" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I311" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15650,7 +15650,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -12993,7 +12993,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -12997,7 +12997,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
         <v>47</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>17</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -6379,45 +6379,49 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr"/>
-      <c r="H121" s="5" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Yousra Saleh</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>32/43</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13044,7 +13048,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13091,7 +13095,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13138,7 +13142,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13858,7 +13862,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14872,7 +14876,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14919,7 +14923,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -14966,7 +14970,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15690,7 +15694,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -13021,7 +13021,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -13045,7 +13045,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -13045,7 +13045,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -96,10 +96,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1345,10 +1345,10 @@
         <v>24</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>26</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>24</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>15</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1658,22 +1658,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -1743,10 +1743,10 @@
         <v>24</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         <v>29</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>29</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2124,475 +2124,475 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Session recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Session recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Session missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Future session</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Session missed</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Future session</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4247,430 +4247,430 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr"/>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr"/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr"/>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr"/>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr"/>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4912,430 +4912,430 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr"/>
+      <c r="H88" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>B1B1</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>ENDOCRINOLOGY</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>0/43</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I89" s="6" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I90" s="6" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr"/>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I91" s="6" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr"/>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr"/>
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I93" s="6" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr"/>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>B1B1</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>ENDOCRINOLOGY</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr"/>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6485,172 +6485,172 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr"/>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr"/>
+      <c r="H123" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>B1B1</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>0/43</t>
+        </is>
+      </c>
+      <c r="I124" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
+      <c r="I125" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr"/>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr"/>
+      <c r="H126" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>B1B1</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
+      <c r="I126" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6751,43 +6751,43 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
+      <c r="C129" s="7" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr"/>
+      <c r="H129" s="7" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I129" s="6" t="inlineStr">
+      <c r="I129" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7029,430 +7029,430 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>B1B2</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>ENDOCRINOLOGY</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr"/>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>0/45</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C137" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr"/>
+      <c r="H137" s="7" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I137" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C138" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F137" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G137" s="6" t="inlineStr"/>
-      <c r="H137" s="6" t="inlineStr">
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr"/>
+      <c r="H138" s="7" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I137" s="6" t="inlineStr">
+      <c r="I138" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C139" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F138" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="6" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr"/>
+      <c r="H139" s="7" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I138" s="6" t="inlineStr">
+      <c r="I139" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C140" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F139" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G139" s="6" t="inlineStr"/>
-      <c r="H139" s="6" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr"/>
+      <c r="H140" s="7" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I139" s="6" t="inlineStr">
+      <c r="I140" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
+      <c r="C141" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F140" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr"/>
+      <c r="H141" s="7" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I140" s="6" t="inlineStr">
+      <c r="I141" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C142" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr"/>
-      <c r="H141" s="6" t="inlineStr">
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr"/>
+      <c r="H142" s="7" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I141" s="6" t="inlineStr">
+      <c r="I142" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr"/>
+      <c r="H143" s="7" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I142" s="6" t="inlineStr">
+      <c r="I143" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="inlineStr"/>
-      <c r="H143" s="6" t="inlineStr">
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr"/>
+      <c r="H144" s="7" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>B1B2</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>ENDOCRINOLOGY</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F144" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
+      <c r="I144" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9275,430 +9275,434 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G185" s="6" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Git Department D Bassant</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>20/50</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>B1C1</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>GASTROENTEROLOGY</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr"/>
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I186" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
+      <c r="C187" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr"/>
+      <c r="H187" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I186" s="6" t="inlineStr">
+      <c r="I187" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="C188" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E187" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr"/>
+      <c r="H188" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I187" s="6" t="inlineStr">
+      <c r="I188" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
+      <c r="C189" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D188" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E188" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr"/>
+      <c r="H189" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I189" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
+      <c r="C190" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D189" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E189" s="6" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G189" s="6" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr"/>
+      <c r="H190" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I190" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
+      <c r="C191" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D190" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E190" s="6" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G190" s="6" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr"/>
+      <c r="H191" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I190" s="6" t="inlineStr">
+      <c r="I191" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C191" s="6" t="inlineStr">
+      <c r="C192" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D191" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F191" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G191" s="6" t="inlineStr"/>
-      <c r="H191" s="6" t="inlineStr">
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr"/>
+      <c r="H192" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I191" s="6" t="inlineStr">
+      <c r="I192" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C192" s="6" t="inlineStr">
+      <c r="C193" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D192" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E192" s="6" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G192" s="6" t="inlineStr"/>
-      <c r="H192" s="6" t="inlineStr">
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr"/>
+      <c r="H193" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I192" s="6" t="inlineStr">
+      <c r="I193" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B193" s="6" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C193" s="6" t="inlineStr">
+      <c r="C194" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D193" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E193" s="6" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F193" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G193" s="6" t="inlineStr"/>
-      <c r="H193" s="6" t="inlineStr">
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr"/>
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
-        <is>
-          <t>B1C1</t>
-        </is>
-      </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>GASTROENTEROLOGY</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F194" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G194" s="6" t="inlineStr"/>
-      <c r="H194" s="6" t="inlineStr">
-        <is>
-          <t>0/50</t>
-        </is>
-      </c>
-      <c r="I194" s="6" t="inlineStr">
+      <c r="I194" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11099,430 +11103,430 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B225" s="6" t="inlineStr">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C225" s="6" t="inlineStr">
+      <c r="C225" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D225" s="6" t="inlineStr">
+      <c r="D225" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E225" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G225" s="6" t="inlineStr"/>
-      <c r="H225" s="6" t="inlineStr">
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr"/>
+      <c r="H225" s="5" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I225" s="6" t="inlineStr">
+      <c r="I225" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>B1C2</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
+        <is>
+          <t>GASTROENTEROLOGY</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr"/>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>0/47</t>
+        </is>
+      </c>
+      <c r="I226" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C226" s="6" t="inlineStr">
+      <c r="C227" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D226" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G226" s="6" t="inlineStr"/>
-      <c r="H226" s="6" t="inlineStr">
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr"/>
+      <c r="H227" s="7" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I226" s="6" t="inlineStr">
+      <c r="I227" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B227" s="6" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C227" s="6" t="inlineStr">
+      <c r="C228" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D227" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E227" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G227" s="6" t="inlineStr"/>
-      <c r="H227" s="6" t="inlineStr">
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr"/>
+      <c r="H228" s="7" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I227" s="6" t="inlineStr">
+      <c r="I228" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B228" s="6" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C228" s="6" t="inlineStr">
+      <c r="C229" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D228" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E228" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F228" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G228" s="6" t="inlineStr"/>
-      <c r="H228" s="6" t="inlineStr">
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr"/>
+      <c r="H229" s="7" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I228" s="6" t="inlineStr">
+      <c r="I229" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B229" s="6" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C229" s="6" t="inlineStr">
+      <c r="C230" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D229" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F229" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G229" s="6" t="inlineStr"/>
-      <c r="H229" s="6" t="inlineStr">
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr"/>
+      <c r="H230" s="7" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I229" s="6" t="inlineStr">
+      <c r="I230" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B230" s="6" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C230" s="6" t="inlineStr">
+      <c r="C231" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D230" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E230" s="6" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F230" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G230" s="6" t="inlineStr"/>
-      <c r="H230" s="6" t="inlineStr">
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr"/>
+      <c r="H231" s="7" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I230" s="6" t="inlineStr">
+      <c r="I231" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B231" s="6" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C231" s="6" t="inlineStr">
+      <c r="C232" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D231" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E231" s="6" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F231" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G231" s="6" t="inlineStr"/>
-      <c r="H231" s="6" t="inlineStr">
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr"/>
+      <c r="H232" s="7" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I231" s="6" t="inlineStr">
+      <c r="I232" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B232" s="6" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C232" s="6" t="inlineStr">
+      <c r="C233" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D232" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E232" s="6" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F232" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G232" s="6" t="inlineStr"/>
-      <c r="H232" s="6" t="inlineStr">
+      <c r="D233" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F233" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="inlineStr"/>
+      <c r="H233" s="7" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I232" s="6" t="inlineStr">
+      <c r="I233" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B233" s="6" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C233" s="6" t="inlineStr">
+      <c r="C234" s="7" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D233" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E233" s="6" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F233" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G233" s="6" t="inlineStr"/>
-      <c r="H233" s="6" t="inlineStr">
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr"/>
+      <c r="H234" s="7" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I233" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B234" s="6" t="inlineStr">
-        <is>
-          <t>B1C2</t>
-        </is>
-      </c>
-      <c r="C234" s="6" t="inlineStr">
-        <is>
-          <t>GASTROENTEROLOGY</t>
-        </is>
-      </c>
-      <c r="D234" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E234" s="6" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F234" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G234" s="6" t="inlineStr"/>
-      <c r="H234" s="6" t="inlineStr">
-        <is>
-          <t>0/47</t>
-        </is>
-      </c>
-      <c r="I234" s="6" t="inlineStr">
+      <c r="I234" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13092,7 +13096,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13139,7 +13143,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13186,7 +13190,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13323,7 +13327,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13370,7 +13374,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13385,215 +13389,215 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B275" s="6" t="inlineStr">
+      <c r="A275" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B275" s="7" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C275" s="6" t="inlineStr">
+      <c r="C275" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D275" s="6" t="inlineStr">
+      <c r="D275" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="E275" s="7" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F275" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G275" s="6" t="inlineStr"/>
-      <c r="H275" s="6" t="inlineStr">
+      <c r="F275" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G275" s="7" t="inlineStr"/>
+      <c r="H275" s="7" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I275" s="6" t="inlineStr">
+      <c r="I275" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B276" s="6" t="inlineStr">
+      <c r="A276" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B276" s="7" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C276" s="6" t="inlineStr">
+      <c r="C276" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D276" s="6" t="inlineStr">
+      <c r="D276" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="E276" s="7" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F276" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G276" s="6" t="inlineStr"/>
-      <c r="H276" s="6" t="inlineStr">
+      <c r="F276" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G276" s="7" t="inlineStr"/>
+      <c r="H276" s="7" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I276" s="6" t="inlineStr">
+      <c r="I276" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B277" s="6" t="inlineStr">
+      <c r="A277" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B277" s="7" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C277" s="6" t="inlineStr">
+      <c r="C277" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D277" s="6" t="inlineStr">
+      <c r="D277" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="E277" s="7" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F277" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G277" s="6" t="inlineStr"/>
-      <c r="H277" s="6" t="inlineStr">
+      <c r="F277" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G277" s="7" t="inlineStr"/>
+      <c r="H277" s="7" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I277" s="6" t="inlineStr">
+      <c r="I277" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B278" s="6" t="inlineStr">
+      <c r="A278" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B278" s="7" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C278" s="6" t="inlineStr">
+      <c r="C278" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D278" s="6" t="inlineStr">
+      <c r="D278" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="E278" s="7" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F278" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G278" s="6" t="inlineStr"/>
-      <c r="H278" s="6" t="inlineStr">
+      <c r="F278" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G278" s="7" t="inlineStr"/>
+      <c r="H278" s="7" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I278" s="6" t="inlineStr">
+      <c r="I278" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B279" s="6" t="inlineStr">
+      <c r="A279" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B279" s="7" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C279" s="6" t="inlineStr">
+      <c r="C279" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D279" s="6" t="inlineStr">
+      <c r="D279" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="E279" s="7" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F279" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G279" s="6" t="inlineStr"/>
-      <c r="H279" s="6" t="inlineStr">
+      <c r="F279" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G279" s="7" t="inlineStr"/>
+      <c r="H279" s="7" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I279" s="6" t="inlineStr">
+      <c r="I279" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13914,7 +13918,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14070,215 +14074,215 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C290" s="6" t="inlineStr">
+      <c r="C290" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D290" s="6" t="inlineStr">
+      <c r="D290" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="E290" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F290" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G290" s="6" t="inlineStr"/>
-      <c r="H290" s="6" t="inlineStr">
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="inlineStr"/>
+      <c r="H290" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I290" s="6" t="inlineStr">
+      <c r="I290" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B291" s="7" t="inlineStr">
+        <is>
+          <t>B1D1</t>
+        </is>
+      </c>
+      <c r="C291" s="7" t="inlineStr">
+        <is>
+          <t>RHEUMATOLOGY</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E291" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F291" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G291" s="7" t="inlineStr"/>
+      <c r="H291" s="7" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I291" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B291" s="6" t="inlineStr">
+    <row r="292">
+      <c r="A292" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B292" s="7" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C291" s="6" t="inlineStr">
+      <c r="C292" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D291" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E291" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F291" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G291" s="6" t="inlineStr"/>
-      <c r="H291" s="6" t="inlineStr">
+      <c r="D292" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E292" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F292" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G292" s="7" t="inlineStr"/>
+      <c r="H292" s="7" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I291" s="6" t="inlineStr">
+      <c r="I292" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B292" s="6" t="inlineStr">
+    <row r="293">
+      <c r="A293" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B293" s="7" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C292" s="6" t="inlineStr">
+      <c r="C293" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D292" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E292" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F292" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G292" s="6" t="inlineStr"/>
-      <c r="H292" s="6" t="inlineStr">
+      <c r="D293" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E293" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F293" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G293" s="7" t="inlineStr"/>
+      <c r="H293" s="7" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I292" s="6" t="inlineStr">
+      <c r="I293" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B293" s="6" t="inlineStr">
+    <row r="294">
+      <c r="A294" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B294" s="7" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C293" s="6" t="inlineStr">
+      <c r="C294" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D293" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E293" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F293" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr"/>
-      <c r="H293" s="6" t="inlineStr">
+      <c r="D294" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E294" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F294" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G294" s="7" t="inlineStr"/>
+      <c r="H294" s="7" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I293" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
-        <is>
-          <t>B1D1</t>
-        </is>
-      </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>RHEUMATOLOGY</t>
-        </is>
-      </c>
-      <c r="D294" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E294" s="6" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G294" s="6" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14928,7 +14932,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14975,7 +14979,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15022,7 +15026,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15159,7 +15163,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15206,7 +15210,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15221,215 +15225,215 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B315" s="6" t="inlineStr">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C315" s="6" t="inlineStr">
+      <c r="C315" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D315" s="6" t="inlineStr">
+      <c r="D315" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="E315" s="5" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="F315" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G315" s="6" t="inlineStr"/>
-      <c r="H315" s="6" t="inlineStr">
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="inlineStr"/>
+      <c r="H315" s="5" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I315" s="6" t="inlineStr">
+      <c r="I315" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B316" s="7" t="inlineStr">
+        <is>
+          <t>B1D2</t>
+        </is>
+      </c>
+      <c r="C316" s="7" t="inlineStr">
+        <is>
+          <t>NEPHROLOGY</t>
+        </is>
+      </c>
+      <c r="D316" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E316" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F316" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G316" s="7" t="inlineStr"/>
+      <c r="H316" s="7" t="inlineStr">
+        <is>
+          <t>0/36</t>
+        </is>
+      </c>
+      <c r="I316" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B316" s="6" t="inlineStr">
+    <row r="317">
+      <c r="A317" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B317" s="7" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C316" s="6" t="inlineStr">
+      <c r="C317" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D316" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E316" s="6" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="F316" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G316" s="6" t="inlineStr"/>
-      <c r="H316" s="6" t="inlineStr">
+      <c r="D317" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E317" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F317" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G317" s="7" t="inlineStr"/>
+      <c r="H317" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I316" s="6" t="inlineStr">
+      <c r="I317" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B317" s="6" t="inlineStr">
+    <row r="318">
+      <c r="A318" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B318" s="7" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C317" s="6" t="inlineStr">
+      <c r="C318" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D317" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E317" s="6" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F317" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G317" s="6" t="inlineStr"/>
-      <c r="H317" s="6" t="inlineStr">
+      <c r="D318" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E318" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F318" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G318" s="7" t="inlineStr"/>
+      <c r="H318" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I317" s="6" t="inlineStr">
+      <c r="I318" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B318" s="6" t="inlineStr">
+    <row r="319">
+      <c r="A319" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B319" s="7" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C318" s="6" t="inlineStr">
+      <c r="C319" s="7" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D318" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E318" s="6" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F318" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G318" s="6" t="inlineStr"/>
-      <c r="H318" s="6" t="inlineStr">
+      <c r="D319" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E319" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F319" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G319" s="7" t="inlineStr"/>
+      <c r="H319" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I318" s="6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B319" s="6" t="inlineStr">
-        <is>
-          <t>B1D2</t>
-        </is>
-      </c>
-      <c r="C319" s="6" t="inlineStr">
-        <is>
-          <t>NEPHROLOGY</t>
-        </is>
-      </c>
-      <c r="D319" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E319" s="6" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F319" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G319" s="6" t="inlineStr"/>
-      <c r="H319" s="6" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I319" s="6" t="inlineStr">
+      <c r="I319" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15750,7 +15754,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15906,215 +15910,215 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B330" s="6" t="inlineStr">
+      <c r="A330" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B330" s="7" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C330" s="6" t="inlineStr">
+      <c r="C330" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D330" s="6" t="inlineStr">
+      <c r="D330" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="E330" s="7" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F330" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G330" s="6" t="inlineStr"/>
-      <c r="H330" s="6" t="inlineStr">
+      <c r="F330" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G330" s="7" t="inlineStr"/>
+      <c r="H330" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I330" s="6" t="inlineStr">
+      <c r="I330" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B331" s="6" t="inlineStr">
+      <c r="A331" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B331" s="7" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C331" s="6" t="inlineStr">
+      <c r="C331" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D331" s="6" t="inlineStr">
+      <c r="D331" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="E331" s="7" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F331" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G331" s="6" t="inlineStr"/>
-      <c r="H331" s="6" t="inlineStr">
+      <c r="F331" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G331" s="7" t="inlineStr"/>
+      <c r="H331" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I331" s="6" t="inlineStr">
+      <c r="I331" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B332" s="6" t="inlineStr">
+      <c r="A332" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B332" s="7" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C332" s="6" t="inlineStr">
+      <c r="C332" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D332" s="6" t="inlineStr">
+      <c r="D332" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="E332" s="7" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F332" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G332" s="6" t="inlineStr"/>
-      <c r="H332" s="6" t="inlineStr">
+      <c r="F332" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G332" s="7" t="inlineStr"/>
+      <c r="H332" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I332" s="6" t="inlineStr">
+      <c r="I332" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B333" s="6" t="inlineStr">
+      <c r="A333" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B333" s="7" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C333" s="6" t="inlineStr">
+      <c r="C333" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D333" s="6" t="inlineStr">
+      <c r="D333" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="E333" s="7" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F333" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G333" s="6" t="inlineStr"/>
-      <c r="H333" s="6" t="inlineStr">
+      <c r="F333" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G333" s="7" t="inlineStr"/>
+      <c r="H333" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I333" s="6" t="inlineStr">
+      <c r="I333" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="6" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B334" s="6" t="inlineStr">
+      <c r="A334" s="7" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B334" s="7" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C334" s="6" t="inlineStr">
+      <c r="C334" s="7" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D334" s="6" t="inlineStr">
+      <c r="D334" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="E334" s="7" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F334" s="6" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G334" s="6" t="inlineStr"/>
-      <c r="H334" s="6" t="inlineStr">
+      <c r="F334" s="7" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G334" s="7" t="inlineStr"/>
+      <c r="H334" s="7" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I334" s="6" t="inlineStr">
+      <c r="I334" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -13065,7 +13065,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -99,10 +99,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -1345,10 +1345,10 @@
         <v>25</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>26</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>25</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>16</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         <v>27</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         <v>25</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         <v>30</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>30</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2186,417 +2186,417 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Session missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Session missed</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Future session</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Future session</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4294,387 +4294,387 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr"/>
-      <c r="H80" s="7" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -4963,387 +4963,387 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>B1B1</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>ENDOCRINOLOGY</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>0/43</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
-      <c r="H92" s="7" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>B1B1</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>ENDOCRINOLOGY</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6536,129 +6536,129 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr"/>
-      <c r="H124" s="7" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I124" s="7" t="inlineStr">
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>B1B1</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>0/43</t>
+        </is>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C126" s="8" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr"/>
-      <c r="H125" s="7" t="inlineStr">
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr"/>
+      <c r="H126" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I125" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>B1B1</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr"/>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I126" s="7" t="inlineStr">
+      <c r="I126" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6759,43 +6759,43 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E129" s="8" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="inlineStr"/>
-      <c r="H129" s="7" t="inlineStr">
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I129" s="7" t="inlineStr">
+      <c r="I129" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7084,387 +7084,387 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="inlineStr"/>
-      <c r="H136" s="7" t="inlineStr">
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I136" s="7" t="inlineStr">
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>B1B2</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>ENDOCRINOLOGY</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>0/45</t>
+        </is>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C137" s="7" t="inlineStr">
+      <c r="C138" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="inlineStr"/>
-      <c r="H137" s="7" t="inlineStr">
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G138" s="8" t="inlineStr"/>
+      <c r="H138" s="8" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I137" s="7" t="inlineStr">
+      <c r="I138" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C138" s="7" t="inlineStr">
+      <c r="C139" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G138" s="7" t="inlineStr"/>
-      <c r="H138" s="7" t="inlineStr">
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I138" s="7" t="inlineStr">
+      <c r="I139" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C139" s="7" t="inlineStr">
+      <c r="C140" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr"/>
-      <c r="H139" s="7" t="inlineStr">
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G140" s="8" t="inlineStr"/>
+      <c r="H140" s="8" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I139" s="7" t="inlineStr">
+      <c r="I140" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B140" s="7" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
+      <c r="C141" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr"/>
-      <c r="H140" s="7" t="inlineStr">
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="8" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I140" s="7" t="inlineStr">
+      <c r="I141" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr">
+      <c r="C142" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr"/>
-      <c r="H141" s="7" t="inlineStr">
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G142" s="8" t="inlineStr"/>
+      <c r="H142" s="8" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I141" s="7" t="inlineStr">
+      <c r="I142" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
+      <c r="C143" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr"/>
-      <c r="H142" s="7" t="inlineStr">
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I142" s="7" t="inlineStr">
+      <c r="I143" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B143" s="7" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C144" s="8" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr"/>
-      <c r="H143" s="7" t="inlineStr">
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr"/>
+      <c r="H144" s="8" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I143" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B144" s="7" t="inlineStr">
-        <is>
-          <t>B1B2</t>
-        </is>
-      </c>
-      <c r="C144" s="7" t="inlineStr">
-        <is>
-          <t>ENDOCRINOLOGY</t>
-        </is>
-      </c>
-      <c r="D144" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr"/>
-      <c r="H144" s="7" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
-      <c r="I144" s="7" t="inlineStr">
+      <c r="I144" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9334,387 +9334,387 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C186" s="7" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D186" s="7" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E186" s="7" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F186" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G186" s="7" t="inlineStr"/>
-      <c r="H186" s="7" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I186" s="7" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>B1C1</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>GASTROENTEROLOGY</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E187" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G187" s="8" t="inlineStr"/>
+      <c r="H187" s="8" t="inlineStr">
+        <is>
+          <t>0/50</t>
+        </is>
+      </c>
+      <c r="I187" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B187" s="7" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C187" s="7" t="inlineStr">
+      <c r="C188" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D187" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="inlineStr"/>
-      <c r="H187" s="7" t="inlineStr">
+      <c r="D188" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G188" s="8" t="inlineStr"/>
+      <c r="H188" s="8" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I187" s="7" t="inlineStr">
+      <c r="I188" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B188" s="7" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C188" s="7" t="inlineStr">
+      <c r="C189" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D188" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E188" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F188" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G188" s="7" t="inlineStr"/>
-      <c r="H188" s="7" t="inlineStr">
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G189" s="8" t="inlineStr"/>
+      <c r="H189" s="8" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I188" s="7" t="inlineStr">
+      <c r="I189" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B189" s="7" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C189" s="7" t="inlineStr">
+      <c r="C190" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D189" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E189" s="7" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G189" s="7" t="inlineStr"/>
-      <c r="H189" s="7" t="inlineStr">
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E190" s="8" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F190" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G190" s="8" t="inlineStr"/>
+      <c r="H190" s="8" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I189" s="7" t="inlineStr">
+      <c r="I190" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B190" s="7" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C190" s="7" t="inlineStr">
+      <c r="C191" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D190" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F190" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G190" s="7" t="inlineStr"/>
-      <c r="H190" s="7" t="inlineStr">
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E191" s="8" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F191" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G191" s="8" t="inlineStr"/>
+      <c r="H191" s="8" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I190" s="7" t="inlineStr">
+      <c r="I191" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B191" s="7" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C191" s="7" t="inlineStr">
+      <c r="C192" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D191" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E191" s="7" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F191" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G191" s="7" t="inlineStr"/>
-      <c r="H191" s="7" t="inlineStr">
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E192" s="8" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G192" s="8" t="inlineStr"/>
+      <c r="H192" s="8" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I191" s="7" t="inlineStr">
+      <c r="I192" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B192" s="7" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C192" s="7" t="inlineStr">
+      <c r="C193" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D192" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E192" s="7" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F192" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G192" s="7" t="inlineStr"/>
-      <c r="H192" s="7" t="inlineStr">
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G193" s="8" t="inlineStr"/>
+      <c r="H193" s="8" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I192" s="7" t="inlineStr">
+      <c r="I193" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B193" s="7" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C193" s="7" t="inlineStr">
+      <c r="C194" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D193" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E193" s="7" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F193" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G193" s="7" t="inlineStr"/>
-      <c r="H193" s="7" t="inlineStr">
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G194" s="8" t="inlineStr"/>
+      <c r="H194" s="8" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I193" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B194" s="7" t="inlineStr">
-        <is>
-          <t>B1C1</t>
-        </is>
-      </c>
-      <c r="C194" s="7" t="inlineStr">
-        <is>
-          <t>GASTROENTEROLOGY</t>
-        </is>
-      </c>
-      <c r="D194" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E194" s="7" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F194" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G194" s="7" t="inlineStr"/>
-      <c r="H194" s="7" t="inlineStr">
-        <is>
-          <t>0/50</t>
-        </is>
-      </c>
-      <c r="I194" s="7" t="inlineStr">
+      <c r="I194" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11162,387 +11162,387 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B226" s="7" t="inlineStr">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C226" s="7" t="inlineStr">
+      <c r="C226" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D226" s="7" t="inlineStr">
+      <c r="D226" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E226" s="7" t="inlineStr">
+      <c r="E226" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F226" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G226" s="7" t="inlineStr"/>
-      <c r="H226" s="7" t="inlineStr">
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr"/>
+      <c r="H226" s="5" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I226" s="7" t="inlineStr">
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>B1C2</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>GASTROENTEROLOGY</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F227" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G227" s="8" t="inlineStr"/>
+      <c r="H227" s="8" t="inlineStr">
+        <is>
+          <t>0/47</t>
+        </is>
+      </c>
+      <c r="I227" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B227" s="7" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C227" s="7" t="inlineStr">
+      <c r="C228" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D227" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E227" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F227" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G227" s="7" t="inlineStr"/>
-      <c r="H227" s="7" t="inlineStr">
+      <c r="D228" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E228" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F228" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G228" s="8" t="inlineStr"/>
+      <c r="H228" s="8" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I227" s="7" t="inlineStr">
+      <c r="I228" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B228" s="7" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C228" s="7" t="inlineStr">
+      <c r="C229" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D228" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E228" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F228" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G228" s="7" t="inlineStr"/>
-      <c r="H228" s="7" t="inlineStr">
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G229" s="8" t="inlineStr"/>
+      <c r="H229" s="8" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I228" s="7" t="inlineStr">
+      <c r="I229" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B229" s="7" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C229" s="7" t="inlineStr">
+      <c r="C230" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D229" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E229" s="7" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F229" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr"/>
-      <c r="H229" s="7" t="inlineStr">
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F230" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G230" s="8" t="inlineStr"/>
+      <c r="H230" s="8" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I229" s="7" t="inlineStr">
+      <c r="I230" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B230" s="7" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C230" s="7" t="inlineStr">
+      <c r="C231" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D230" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E230" s="7" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F230" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G230" s="7" t="inlineStr"/>
-      <c r="H230" s="7" t="inlineStr">
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G231" s="8" t="inlineStr"/>
+      <c r="H231" s="8" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I230" s="7" t="inlineStr">
+      <c r="I231" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B231" s="7" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B232" s="8" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C231" s="7" t="inlineStr">
+      <c r="C232" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D231" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E231" s="7" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F231" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G231" s="7" t="inlineStr"/>
-      <c r="H231" s="7" t="inlineStr">
+      <c r="D232" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E232" s="8" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F232" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G232" s="8" t="inlineStr"/>
+      <c r="H232" s="8" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I231" s="7" t="inlineStr">
+      <c r="I232" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B232" s="7" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C232" s="7" t="inlineStr">
+      <c r="C233" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D232" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E232" s="7" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F232" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G232" s="7" t="inlineStr"/>
-      <c r="H232" s="7" t="inlineStr">
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E233" s="8" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G233" s="8" t="inlineStr"/>
+      <c r="H233" s="8" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I232" s="7" t="inlineStr">
+      <c r="I233" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B233" s="7" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B234" s="8" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C233" s="7" t="inlineStr">
+      <c r="C234" s="8" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D233" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E233" s="7" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F233" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G233" s="7" t="inlineStr"/>
-      <c r="H233" s="7" t="inlineStr">
+      <c r="D234" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E234" s="8" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F234" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G234" s="8" t="inlineStr"/>
+      <c r="H234" s="8" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I233" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B234" s="7" t="inlineStr">
-        <is>
-          <t>B1C2</t>
-        </is>
-      </c>
-      <c r="C234" s="7" t="inlineStr">
-        <is>
-          <t>GASTROENTEROLOGY</t>
-        </is>
-      </c>
-      <c r="D234" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E234" s="7" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F234" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G234" s="7" t="inlineStr"/>
-      <c r="H234" s="7" t="inlineStr">
-        <is>
-          <t>0/47</t>
-        </is>
-      </c>
-      <c r="I234" s="7" t="inlineStr">
+      <c r="I234" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13405,215 +13405,215 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B275" s="7" t="inlineStr">
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B275" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C275" s="7" t="inlineStr">
+      <c r="C275" s="8" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D275" s="7" t="inlineStr">
+      <c r="D275" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E275" s="7" t="inlineStr">
+      <c r="E275" s="8" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F275" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G275" s="7" t="inlineStr"/>
-      <c r="H275" s="7" t="inlineStr">
+      <c r="F275" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G275" s="8" t="inlineStr"/>
+      <c r="H275" s="8" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I275" s="7" t="inlineStr">
+      <c r="I275" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B276" s="7" t="inlineStr">
+      <c r="A276" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B276" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C276" s="7" t="inlineStr">
+      <c r="C276" s="8" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D276" s="7" t="inlineStr">
+      <c r="D276" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E276" s="7" t="inlineStr">
+      <c r="E276" s="8" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F276" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G276" s="7" t="inlineStr"/>
-      <c r="H276" s="7" t="inlineStr">
+      <c r="F276" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G276" s="8" t="inlineStr"/>
+      <c r="H276" s="8" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I276" s="7" t="inlineStr">
+      <c r="I276" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B277" s="7" t="inlineStr">
+      <c r="A277" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B277" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C277" s="7" t="inlineStr">
+      <c r="C277" s="8" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D277" s="7" t="inlineStr">
+      <c r="D277" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E277" s="7" t="inlineStr">
+      <c r="E277" s="8" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F277" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G277" s="7" t="inlineStr"/>
-      <c r="H277" s="7" t="inlineStr">
+      <c r="F277" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G277" s="8" t="inlineStr"/>
+      <c r="H277" s="8" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I277" s="7" t="inlineStr">
+      <c r="I277" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B278" s="7" t="inlineStr">
+      <c r="A278" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B278" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C278" s="7" t="inlineStr">
+      <c r="C278" s="8" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D278" s="7" t="inlineStr">
+      <c r="D278" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E278" s="7" t="inlineStr">
+      <c r="E278" s="8" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F278" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G278" s="7" t="inlineStr"/>
-      <c r="H278" s="7" t="inlineStr">
+      <c r="F278" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G278" s="8" t="inlineStr"/>
+      <c r="H278" s="8" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I278" s="7" t="inlineStr">
+      <c r="I278" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B279" s="7" t="inlineStr">
+      <c r="A279" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C279" s="7" t="inlineStr">
+      <c r="C279" s="8" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D279" s="7" t="inlineStr">
+      <c r="D279" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E279" s="7" t="inlineStr">
+      <c r="E279" s="8" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F279" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G279" s="7" t="inlineStr"/>
-      <c r="H279" s="7" t="inlineStr">
+      <c r="F279" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G279" s="8" t="inlineStr"/>
+      <c r="H279" s="8" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I279" s="7" t="inlineStr">
+      <c r="I279" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14137,172 +14137,172 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B291" s="7" t="inlineStr">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C291" s="7" t="inlineStr">
+      <c r="C291" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D291" s="7" t="inlineStr">
+      <c r="D291" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E291" s="7" t="inlineStr">
+      <c r="E291" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F291" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G291" s="7" t="inlineStr"/>
-      <c r="H291" s="7" t="inlineStr">
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G291" s="5" t="inlineStr"/>
+      <c r="H291" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I291" s="7" t="inlineStr">
+      <c r="I291" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B292" s="8" t="inlineStr">
+        <is>
+          <t>B1D1</t>
+        </is>
+      </c>
+      <c r="C292" s="8" t="inlineStr">
+        <is>
+          <t>RHEUMATOLOGY</t>
+        </is>
+      </c>
+      <c r="D292" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E292" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F292" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G292" s="8" t="inlineStr"/>
+      <c r="H292" s="8" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I292" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B292" s="7" t="inlineStr">
+    <row r="293">
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C292" s="7" t="inlineStr">
+      <c r="C293" s="8" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D292" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E292" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F292" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G292" s="7" t="inlineStr"/>
-      <c r="H292" s="7" t="inlineStr">
+      <c r="D293" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E293" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F293" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G293" s="8" t="inlineStr"/>
+      <c r="H293" s="8" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I292" s="7" t="inlineStr">
+      <c r="I293" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B293" s="7" t="inlineStr">
+    <row r="294">
+      <c r="A294" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B294" s="8" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C293" s="7" t="inlineStr">
+      <c r="C294" s="8" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D293" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E293" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F293" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G293" s="7" t="inlineStr"/>
-      <c r="H293" s="7" t="inlineStr">
+      <c r="D294" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E294" s="8" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F294" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G294" s="8" t="inlineStr"/>
+      <c r="H294" s="8" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I293" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B294" s="7" t="inlineStr">
-        <is>
-          <t>B1D1</t>
-        </is>
-      </c>
-      <c r="C294" s="7" t="inlineStr">
-        <is>
-          <t>RHEUMATOLOGY</t>
-        </is>
-      </c>
-      <c r="D294" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E294" s="7" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F294" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G294" s="7" t="inlineStr"/>
-      <c r="H294" s="7" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I294" s="7" t="inlineStr">
+      <c r="I294" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15292,172 +15292,172 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B316" s="7" t="inlineStr">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C316" s="7" t="inlineStr">
+      <c r="C316" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D316" s="7" t="inlineStr">
+      <c r="D316" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E316" s="7" t="inlineStr">
+      <c r="E316" s="5" t="inlineStr">
         <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="F316" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G316" s="7" t="inlineStr"/>
-      <c r="H316" s="7" t="inlineStr">
+      <c r="F316" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G316" s="5" t="inlineStr"/>
+      <c r="H316" s="5" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I316" s="7" t="inlineStr">
+      <c r="I316" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B317" s="8" t="inlineStr">
+        <is>
+          <t>B1D2</t>
+        </is>
+      </c>
+      <c r="C317" s="8" t="inlineStr">
+        <is>
+          <t>NEPHROLOGY</t>
+        </is>
+      </c>
+      <c r="D317" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E317" s="8" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F317" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G317" s="8" t="inlineStr"/>
+      <c r="H317" s="8" t="inlineStr">
+        <is>
+          <t>0/36</t>
+        </is>
+      </c>
+      <c r="I317" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B317" s="7" t="inlineStr">
+    <row r="318">
+      <c r="A318" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B318" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C317" s="7" t="inlineStr">
+      <c r="C318" s="8" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D317" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E317" s="7" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="F317" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G317" s="7" t="inlineStr"/>
-      <c r="H317" s="7" t="inlineStr">
+      <c r="D318" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E318" s="8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F318" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G318" s="8" t="inlineStr"/>
+      <c r="H318" s="8" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I317" s="7" t="inlineStr">
+      <c r="I318" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B318" s="7" t="inlineStr">
+    <row r="319">
+      <c r="A319" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B319" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C318" s="7" t="inlineStr">
+      <c r="C319" s="8" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D318" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E318" s="7" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F318" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G318" s="7" t="inlineStr"/>
-      <c r="H318" s="7" t="inlineStr">
+      <c r="D319" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F319" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G319" s="8" t="inlineStr"/>
+      <c r="H319" s="8" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I318" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B319" s="7" t="inlineStr">
-        <is>
-          <t>B1D2</t>
-        </is>
-      </c>
-      <c r="C319" s="7" t="inlineStr">
-        <is>
-          <t>NEPHROLOGY</t>
-        </is>
-      </c>
-      <c r="D319" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E319" s="7" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F319" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G319" s="7" t="inlineStr"/>
-      <c r="H319" s="7" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I319" s="7" t="inlineStr">
+      <c r="I319" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15934,215 +15934,215 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B330" s="7" t="inlineStr">
+      <c r="A330" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B330" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C330" s="7" t="inlineStr">
+      <c r="C330" s="8" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D330" s="7" t="inlineStr">
+      <c r="D330" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E330" s="7" t="inlineStr">
+      <c r="E330" s="8" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F330" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G330" s="7" t="inlineStr"/>
-      <c r="H330" s="7" t="inlineStr">
+      <c r="F330" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G330" s="8" t="inlineStr"/>
+      <c r="H330" s="8" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I330" s="7" t="inlineStr">
+      <c r="I330" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B331" s="7" t="inlineStr">
+      <c r="A331" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B331" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C331" s="7" t="inlineStr">
+      <c r="C331" s="8" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D331" s="7" t="inlineStr">
+      <c r="D331" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E331" s="7" t="inlineStr">
+      <c r="E331" s="8" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F331" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G331" s="7" t="inlineStr"/>
-      <c r="H331" s="7" t="inlineStr">
+      <c r="F331" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G331" s="8" t="inlineStr"/>
+      <c r="H331" s="8" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I331" s="7" t="inlineStr">
+      <c r="I331" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B332" s="7" t="inlineStr">
+      <c r="A332" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B332" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C332" s="7" t="inlineStr">
+      <c r="C332" s="8" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D332" s="7" t="inlineStr">
+      <c r="D332" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E332" s="7" t="inlineStr">
+      <c r="E332" s="8" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F332" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G332" s="7" t="inlineStr"/>
-      <c r="H332" s="7" t="inlineStr">
+      <c r="F332" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G332" s="8" t="inlineStr"/>
+      <c r="H332" s="8" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I332" s="7" t="inlineStr">
+      <c r="I332" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B333" s="7" t="inlineStr">
+      <c r="A333" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B333" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C333" s="7" t="inlineStr">
+      <c r="C333" s="8" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D333" s="7" t="inlineStr">
+      <c r="D333" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E333" s="7" t="inlineStr">
+      <c r="E333" s="8" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F333" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G333" s="7" t="inlineStr"/>
-      <c r="H333" s="7" t="inlineStr">
+      <c r="F333" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G333" s="8" t="inlineStr"/>
+      <c r="H333" s="8" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I333" s="7" t="inlineStr">
+      <c r="I333" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="7" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B334" s="7" t="inlineStr">
+      <c r="A334" s="8" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B334" s="8" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C334" s="7" t="inlineStr">
+      <c r="C334" s="8" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D334" s="7" t="inlineStr">
+      <c r="D334" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E334" s="7" t="inlineStr">
+      <c r="E334" s="8" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F334" s="7" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G334" s="7" t="inlineStr"/>
-      <c r="H334" s="7" t="inlineStr">
+      <c r="F334" s="8" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G334" s="8" t="inlineStr"/>
+      <c r="H334" s="8" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I334" s="7" t="inlineStr">
+      <c r="I334" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -102,10 +102,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1345,10 +1345,10 @@
         <v>26</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         <v>28</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>26</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>17</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         <v>29</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         <v>27</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         <v>31</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         <v>31</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2248,359 +2248,359 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Future session</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>B1A1</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>0/42</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Future session</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>0/42</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>B1A1</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4349,344 +4349,344 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>B1A2</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr"/>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>0/44</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr"/>
+      <c r="H77" s="9" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="I78" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="I80" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>NEUROLOGY</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G80" s="8" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>PHYSICAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr"/>
+      <c r="H81" s="9" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
+      <c r="I81" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr">
         <is>
           <t>0/44</t>
         </is>
       </c>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>B1A2</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>PHYSICAL MEDICINE</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="inlineStr"/>
-      <c r="H82" s="8" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="I82" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -5022,344 +5022,344 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>B1B1</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>ENDOCRINOLOGY</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>0/43</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C92" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr"/>
+      <c r="H92" s="9" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="I92" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr"/>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="I93" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C94" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="8" t="inlineStr">
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
+      <c r="I94" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I94" s="8" t="inlineStr">
+      <c r="I95" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F95" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="8" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr"/>
+      <c r="H96" s="9" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I95" s="8" t="inlineStr">
+      <c r="I96" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>B1B1</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
-        <is>
-          <t>ENDOCRINOLOGY</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="8" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="I97" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6595,86 +6595,86 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D125" s="8" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F125" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="8" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I125" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C126" s="8" t="inlineStr">
+      <c r="C126" s="9" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D126" s="8" t="inlineStr">
+      <c r="D126" s="9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E126" s="8" t="inlineStr">
+      <c r="E126" s="9" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F126" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G126" s="8" t="inlineStr"/>
-      <c r="H126" s="8" t="inlineStr">
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="I126" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -6775,43 +6775,43 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D129" s="8" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F129" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="8" t="inlineStr">
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr">
         <is>
           <t>0/43</t>
         </is>
       </c>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="I129" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -7147,344 +7147,344 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C137" s="8" t="inlineStr">
+      <c r="C137" s="5" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D137" s="8" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E137" s="8" t="inlineStr">
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="8" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr"/>
+      <c r="H137" s="5" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I137" s="8" t="inlineStr">
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>B1B2</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>ENDOCRINOLOGY</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr"/>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>0/45</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C138" s="8" t="inlineStr">
+      <c r="C139" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F138" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G138" s="8" t="inlineStr"/>
-      <c r="H138" s="8" t="inlineStr">
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr"/>
+      <c r="H139" s="9" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I138" s="8" t="inlineStr">
+      <c r="I139" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C139" s="8" t="inlineStr">
+      <c r="C140" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D139" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F139" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="8" t="inlineStr">
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr"/>
+      <c r="H140" s="9" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I139" s="8" t="inlineStr">
+      <c r="I140" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C140" s="8" t="inlineStr">
+      <c r="C141" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D140" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E140" s="8" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F140" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G140" s="8" t="inlineStr"/>
-      <c r="H140" s="8" t="inlineStr">
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr"/>
+      <c r="H141" s="9" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="I141" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B141" s="8" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C141" s="8" t="inlineStr">
+      <c r="C142" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D141" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E141" s="8" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F141" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr"/>
-      <c r="H141" s="8" t="inlineStr">
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr"/>
+      <c r="H142" s="9" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I141" s="8" t="inlineStr">
+      <c r="I142" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C142" s="8" t="inlineStr">
+      <c r="C143" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D142" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F142" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G142" s="8" t="inlineStr"/>
-      <c r="H142" s="8" t="inlineStr">
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr"/>
+      <c r="H143" s="9" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I142" s="8" t="inlineStr">
+      <c r="I143" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C143" s="8" t="inlineStr">
+      <c r="C144" s="9" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D143" s="8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr"/>
-      <c r="H143" s="8" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr"/>
+      <c r="H144" s="9" t="inlineStr">
         <is>
           <t>0/45</t>
         </is>
       </c>
-      <c r="I143" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>B1B2</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr">
-        <is>
-          <t>ENDOCRINOLOGY</t>
-        </is>
-      </c>
-      <c r="D144" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F144" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G144" s="8" t="inlineStr"/>
-      <c r="H144" s="8" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="I144" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9401,344 +9401,344 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C187" s="8" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D187" s="8" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E187" s="8" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F187" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G187" s="8" t="inlineStr"/>
-      <c r="H187" s="8" t="inlineStr">
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr"/>
+      <c r="H187" s="5" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I187" s="8" t="inlineStr">
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B188" s="9" t="inlineStr">
+        <is>
+          <t>B1C1</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>GASTROENTEROLOGY</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E188" s="9" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F188" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G188" s="9" t="inlineStr"/>
+      <c r="H188" s="9" t="inlineStr">
+        <is>
+          <t>0/50</t>
+        </is>
+      </c>
+      <c r="I188" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B188" s="8" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C188" s="8" t="inlineStr">
+      <c r="C189" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D188" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E188" s="8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F188" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G188" s="8" t="inlineStr"/>
-      <c r="H188" s="8" t="inlineStr">
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G189" s="9" t="inlineStr"/>
+      <c r="H189" s="9" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I188" s="8" t="inlineStr">
+      <c r="I189" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B189" s="8" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B190" s="9" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C189" s="8" t="inlineStr">
+      <c r="C190" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D189" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E189" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F189" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G189" s="8" t="inlineStr"/>
-      <c r="H189" s="8" t="inlineStr">
+      <c r="D190" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E190" s="9" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="inlineStr"/>
+      <c r="H190" s="9" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I189" s="8" t="inlineStr">
+      <c r="I190" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B190" s="8" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B191" s="9" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C190" s="8" t="inlineStr">
+      <c r="C191" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D190" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E190" s="8" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F190" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G190" s="8" t="inlineStr"/>
-      <c r="H190" s="8" t="inlineStr">
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E191" s="9" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F191" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G191" s="9" t="inlineStr"/>
+      <c r="H191" s="9" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I190" s="8" t="inlineStr">
+      <c r="I191" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B191" s="8" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B192" s="9" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C191" s="8" t="inlineStr">
+      <c r="C192" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D191" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E191" s="8" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F191" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G191" s="8" t="inlineStr"/>
-      <c r="H191" s="8" t="inlineStr">
+      <c r="D192" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E192" s="9" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F192" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G192" s="9" t="inlineStr"/>
+      <c r="H192" s="9" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I191" s="8" t="inlineStr">
+      <c r="I192" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B192" s="8" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C192" s="8" t="inlineStr">
+      <c r="C193" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D192" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E192" s="8" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F192" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G192" s="8" t="inlineStr"/>
-      <c r="H192" s="8" t="inlineStr">
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E193" s="9" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F193" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G193" s="9" t="inlineStr"/>
+      <c r="H193" s="9" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I192" s="8" t="inlineStr">
+      <c r="I193" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B193" s="8" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C193" s="8" t="inlineStr">
+      <c r="C194" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D193" s="8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E193" s="8" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F193" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G193" s="8" t="inlineStr"/>
-      <c r="H193" s="8" t="inlineStr">
+      <c r="D194" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E194" s="9" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F194" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G194" s="9" t="inlineStr"/>
+      <c r="H194" s="9" t="inlineStr">
         <is>
           <t>0/50</t>
         </is>
       </c>
-      <c r="I193" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B194" s="8" t="inlineStr">
-        <is>
-          <t>B1C1</t>
-        </is>
-      </c>
-      <c r="C194" s="8" t="inlineStr">
-        <is>
-          <t>GASTROENTEROLOGY</t>
-        </is>
-      </c>
-      <c r="D194" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E194" s="8" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F194" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G194" s="8" t="inlineStr"/>
-      <c r="H194" s="8" t="inlineStr">
-        <is>
-          <t>0/50</t>
-        </is>
-      </c>
-      <c r="I194" s="8" t="inlineStr">
+      <c r="I194" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11237,344 +11237,344 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B227" s="8" t="inlineStr">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C227" s="8" t="inlineStr">
+      <c r="C227" s="5" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D227" s="8" t="inlineStr">
+      <c r="D227" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E227" s="8" t="inlineStr">
+      <c r="E227" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F227" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G227" s="8" t="inlineStr"/>
-      <c r="H227" s="8" t="inlineStr">
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr"/>
+      <c r="H227" s="5" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I227" s="8" t="inlineStr">
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B228" s="9" t="inlineStr">
+        <is>
+          <t>B1C2</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>GASTROENTEROLOGY</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E228" s="9" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G228" s="9" t="inlineStr"/>
+      <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>0/47</t>
+        </is>
+      </c>
+      <c r="I228" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B228" s="8" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C228" s="8" t="inlineStr">
+      <c r="C229" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D228" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E228" s="8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F228" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G228" s="8" t="inlineStr"/>
-      <c r="H228" s="8" t="inlineStr">
+      <c r="D229" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E229" s="9" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G229" s="9" t="inlineStr"/>
+      <c r="H229" s="9" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I228" s="8" t="inlineStr">
+      <c r="I229" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B229" s="8" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B230" s="9" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C229" s="8" t="inlineStr">
+      <c r="C230" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D229" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E229" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F229" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G229" s="8" t="inlineStr"/>
-      <c r="H229" s="8" t="inlineStr">
+      <c r="D230" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E230" s="9" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr"/>
+      <c r="H230" s="9" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I229" s="8" t="inlineStr">
+      <c r="I230" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B230" s="8" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C230" s="8" t="inlineStr">
+      <c r="C231" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D230" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E230" s="8" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="F230" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G230" s="8" t="inlineStr"/>
-      <c r="H230" s="8" t="inlineStr">
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E231" s="9" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr"/>
+      <c r="H231" s="9" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I230" s="8" t="inlineStr">
+      <c r="I231" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B231" s="8" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B232" s="9" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C231" s="8" t="inlineStr">
+      <c r="C232" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D231" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E231" s="8" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="F231" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G231" s="8" t="inlineStr"/>
-      <c r="H231" s="8" t="inlineStr">
+      <c r="D232" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E232" s="9" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G232" s="9" t="inlineStr"/>
+      <c r="H232" s="9" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I231" s="8" t="inlineStr">
+      <c r="I232" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B232" s="8" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C232" s="8" t="inlineStr">
+      <c r="C233" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D232" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E232" s="8" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="F232" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G232" s="8" t="inlineStr"/>
-      <c r="H232" s="8" t="inlineStr">
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E233" s="9" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G233" s="9" t="inlineStr"/>
+      <c r="H233" s="9" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I232" s="8" t="inlineStr">
+      <c r="I233" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B233" s="8" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B234" s="9" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C233" s="8" t="inlineStr">
+      <c r="C234" s="9" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D233" s="8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E233" s="8" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="F233" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G233" s="8" t="inlineStr"/>
-      <c r="H233" s="8" t="inlineStr">
+      <c r="D234" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E234" s="9" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G234" s="9" t="inlineStr"/>
+      <c r="H234" s="9" t="inlineStr">
         <is>
           <t>0/47</t>
         </is>
       </c>
-      <c r="I233" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B234" s="8" t="inlineStr">
-        <is>
-          <t>B1C2</t>
-        </is>
-      </c>
-      <c r="C234" s="8" t="inlineStr">
-        <is>
-          <t>GASTROENTEROLOGY</t>
-        </is>
-      </c>
-      <c r="D234" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E234" s="8" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="F234" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G234" s="8" t="inlineStr"/>
-      <c r="H234" s="8" t="inlineStr">
-        <is>
-          <t>0/47</t>
-        </is>
-      </c>
-      <c r="I234" s="8" t="inlineStr">
+      <c r="I234" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13441,215 +13441,215 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B275" s="8" t="inlineStr">
+      <c r="A275" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B275" s="9" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C275" s="8" t="inlineStr">
+      <c r="C275" s="9" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D275" s="8" t="inlineStr">
+      <c r="D275" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E275" s="8" t="inlineStr">
+      <c r="E275" s="9" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F275" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G275" s="8" t="inlineStr"/>
-      <c r="H275" s="8" t="inlineStr">
+      <c r="F275" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G275" s="9" t="inlineStr"/>
+      <c r="H275" s="9" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I275" s="8" t="inlineStr">
+      <c r="I275" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B276" s="8" t="inlineStr">
+      <c r="A276" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B276" s="9" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C276" s="8" t="inlineStr">
+      <c r="C276" s="9" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D276" s="8" t="inlineStr">
+      <c r="D276" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E276" s="8" t="inlineStr">
+      <c r="E276" s="9" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F276" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G276" s="8" t="inlineStr"/>
-      <c r="H276" s="8" t="inlineStr">
+      <c r="F276" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G276" s="9" t="inlineStr"/>
+      <c r="H276" s="9" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I276" s="8" t="inlineStr">
+      <c r="I276" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B277" s="8" t="inlineStr">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C277" s="8" t="inlineStr">
+      <c r="C277" s="9" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D277" s="8" t="inlineStr">
+      <c r="D277" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E277" s="8" t="inlineStr">
+      <c r="E277" s="9" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F277" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G277" s="8" t="inlineStr"/>
-      <c r="H277" s="8" t="inlineStr">
+      <c r="F277" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G277" s="9" t="inlineStr"/>
+      <c r="H277" s="9" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I277" s="8" t="inlineStr">
+      <c r="I277" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B278" s="8" t="inlineStr">
+      <c r="A278" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B278" s="9" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C278" s="8" t="inlineStr">
+      <c r="C278" s="9" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D278" s="8" t="inlineStr">
+      <c r="D278" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E278" s="8" t="inlineStr">
+      <c r="E278" s="9" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F278" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G278" s="8" t="inlineStr"/>
-      <c r="H278" s="8" t="inlineStr">
+      <c r="F278" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G278" s="9" t="inlineStr"/>
+      <c r="H278" s="9" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I278" s="8" t="inlineStr">
+      <c r="I278" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B279" s="8" t="inlineStr">
+      <c r="A279" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B279" s="9" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C279" s="8" t="inlineStr">
+      <c r="C279" s="9" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D279" s="8" t="inlineStr">
+      <c r="D279" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E279" s="8" t="inlineStr">
+      <c r="E279" s="9" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F279" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G279" s="8" t="inlineStr"/>
-      <c r="H279" s="8" t="inlineStr">
+      <c r="F279" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G279" s="9" t="inlineStr"/>
+      <c r="H279" s="9" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I279" s="8" t="inlineStr">
+      <c r="I279" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14220,129 +14220,129 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B292" s="8" t="inlineStr">
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C292" s="8" t="inlineStr">
+      <c r="C292" s="5" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D292" s="8" t="inlineStr">
+      <c r="D292" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E292" s="8" t="inlineStr">
+      <c r="E292" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F292" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G292" s="8" t="inlineStr"/>
-      <c r="H292" s="8" t="inlineStr">
+      <c r="F292" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G292" s="5" t="inlineStr"/>
+      <c r="H292" s="5" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I292" s="8" t="inlineStr">
+      <c r="I292" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B293" s="9" t="inlineStr">
+        <is>
+          <t>B1D1</t>
+        </is>
+      </c>
+      <c r="C293" s="9" t="inlineStr">
+        <is>
+          <t>RHEUMATOLOGY</t>
+        </is>
+      </c>
+      <c r="D293" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E293" s="9" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F293" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G293" s="9" t="inlineStr"/>
+      <c r="H293" s="9" t="inlineStr">
+        <is>
+          <t>0/28</t>
+        </is>
+      </c>
+      <c r="I293" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B293" s="8" t="inlineStr">
+    <row r="294">
+      <c r="A294" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B294" s="9" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C293" s="8" t="inlineStr">
+      <c r="C294" s="9" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D293" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E293" s="8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F293" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G293" s="8" t="inlineStr"/>
-      <c r="H293" s="8" t="inlineStr">
+      <c r="D294" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E294" s="9" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F294" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G294" s="9" t="inlineStr"/>
+      <c r="H294" s="9" t="inlineStr">
         <is>
           <t>0/28</t>
         </is>
       </c>
-      <c r="I293" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B294" s="8" t="inlineStr">
-        <is>
-          <t>B1D1</t>
-        </is>
-      </c>
-      <c r="C294" s="8" t="inlineStr">
-        <is>
-          <t>RHEUMATOLOGY</t>
-        </is>
-      </c>
-      <c r="D294" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E294" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F294" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G294" s="8" t="inlineStr"/>
-      <c r="H294" s="8" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I294" s="8" t="inlineStr">
+      <c r="I294" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15379,129 +15379,129 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B317" s="8" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C317" s="8" t="inlineStr">
+      <c r="C317" s="5" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D317" s="8" t="inlineStr">
+      <c r="D317" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E317" s="8" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="F317" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G317" s="8" t="inlineStr"/>
-      <c r="H317" s="8" t="inlineStr">
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr"/>
+      <c r="H317" s="5" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I317" s="8" t="inlineStr">
+      <c r="I317" s="5" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B318" s="9" t="inlineStr">
+        <is>
+          <t>B1D2</t>
+        </is>
+      </c>
+      <c r="C318" s="9" t="inlineStr">
+        <is>
+          <t>NEPHROLOGY</t>
+        </is>
+      </c>
+      <c r="D318" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E318" s="9" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F318" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G318" s="9" t="inlineStr"/>
+      <c r="H318" s="9" t="inlineStr">
+        <is>
+          <t>0/36</t>
+        </is>
+      </c>
+      <c r="I318" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B318" s="8" t="inlineStr">
+    <row r="319">
+      <c r="A319" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B319" s="9" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C318" s="8" t="inlineStr">
+      <c r="C319" s="9" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D318" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E318" s="8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="F318" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G318" s="8" t="inlineStr"/>
-      <c r="H318" s="8" t="inlineStr">
+      <c r="D319" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E319" s="9" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F319" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G319" s="9" t="inlineStr"/>
+      <c r="H319" s="9" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I318" s="8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B319" s="8" t="inlineStr">
-        <is>
-          <t>B1D2</t>
-        </is>
-      </c>
-      <c r="C319" s="8" t="inlineStr">
-        <is>
-          <t>NEPHROLOGY</t>
-        </is>
-      </c>
-      <c r="D319" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E319" s="8" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="F319" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G319" s="8" t="inlineStr"/>
-      <c r="H319" s="8" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I319" s="8" t="inlineStr">
+      <c r="I319" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15978,215 +15978,215 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B330" s="8" t="inlineStr">
+      <c r="A330" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B330" s="9" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C330" s="8" t="inlineStr">
+      <c r="C330" s="9" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D330" s="8" t="inlineStr">
+      <c r="D330" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E330" s="8" t="inlineStr">
+      <c r="E330" s="9" t="inlineStr">
         <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="F330" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G330" s="8" t="inlineStr"/>
-      <c r="H330" s="8" t="inlineStr">
+      <c r="F330" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G330" s="9" t="inlineStr"/>
+      <c r="H330" s="9" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I330" s="8" t="inlineStr">
+      <c r="I330" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B331" s="8" t="inlineStr">
+      <c r="A331" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B331" s="9" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C331" s="8" t="inlineStr">
+      <c r="C331" s="9" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D331" s="8" t="inlineStr">
+      <c r="D331" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E331" s="8" t="inlineStr">
+      <c r="E331" s="9" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="F331" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G331" s="8" t="inlineStr"/>
-      <c r="H331" s="8" t="inlineStr">
+      <c r="F331" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G331" s="9" t="inlineStr"/>
+      <c r="H331" s="9" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I331" s="8" t="inlineStr">
+      <c r="I331" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B332" s="8" t="inlineStr">
+      <c r="A332" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B332" s="9" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C332" s="8" t="inlineStr">
+      <c r="C332" s="9" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D332" s="8" t="inlineStr">
+      <c r="D332" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E332" s="8" t="inlineStr">
+      <c r="E332" s="9" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F332" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G332" s="8" t="inlineStr"/>
-      <c r="H332" s="8" t="inlineStr">
+      <c r="F332" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G332" s="9" t="inlineStr"/>
+      <c r="H332" s="9" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I332" s="8" t="inlineStr">
+      <c r="I332" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B333" s="8" t="inlineStr">
+      <c r="A333" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B333" s="9" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C333" s="8" t="inlineStr">
+      <c r="C333" s="9" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D333" s="8" t="inlineStr">
+      <c r="D333" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E333" s="8" t="inlineStr">
+      <c r="E333" s="9" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F333" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G333" s="8" t="inlineStr"/>
-      <c r="H333" s="8" t="inlineStr">
+      <c r="F333" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G333" s="9" t="inlineStr"/>
+      <c r="H333" s="9" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I333" s="8" t="inlineStr">
+      <c r="I333" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="8" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B334" s="8" t="inlineStr">
+      <c r="A334" s="9" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B334" s="9" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C334" s="8" t="inlineStr">
+      <c r="C334" s="9" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D334" s="8" t="inlineStr">
+      <c r="D334" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E334" s="8" t="inlineStr">
+      <c r="E334" s="9" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F334" s="8" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G334" s="8" t="inlineStr"/>
-      <c r="H334" s="8" t="inlineStr">
+      <c r="F334" s="9" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G334" s="9" t="inlineStr"/>
+      <c r="H334" s="9" t="inlineStr">
         <is>
           <t>0/36</t>
         </is>
       </c>
-      <c r="I334" s="8" t="inlineStr">
+      <c r="I334" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1424,22 @@
         <v>46</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -1658,22 +1658,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -1818,22 +1818,22 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>75.6%</t>
         </is>
       </c>
     </row>
@@ -1900,22 +1900,22 @@
         <v>40</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>6</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2310,45 +2310,49 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>38/42</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4389,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4400,45 +4404,49 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>39/44</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9464,45 +9472,49 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C188" s="5" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E188" s="5" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
-        <is>
-          <t>0/50</t>
-        </is>
-      </c>
-      <c r="I188" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Yousra, Git Department D Bassant</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>46/50</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11336,12 +11348,12 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>11/47</t>
+          <t>43/47</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
@@ -13129,7 +13141,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13763,7 +13775,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13810,7 +13822,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13998,7 +14010,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14045,7 +14057,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14295,45 +14307,49 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B293" s="5" t="inlineStr">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C293" s="5" t="inlineStr">
+      <c r="C293" s="2" t="inlineStr">
         <is>
           <t>RHEUMATOLOGY</t>
         </is>
       </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="D293" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E293" s="5" t="inlineStr">
+      <c r="E293" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F293" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G293" s="5" t="inlineStr"/>
-      <c r="H293" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I293" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Tasneem El-Sayed</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14993,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15458,45 +15474,49 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B318" s="5" t="inlineStr">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C318" s="5" t="inlineStr">
+      <c r="C318" s="2" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D318" s="5" t="inlineStr">
+      <c r="D318" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E318" s="5" t="inlineStr">
+      <c r="E318" s="2" t="inlineStr">
         <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="F318" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G318" s="5" t="inlineStr"/>
-      <c r="H318" s="5" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I318" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>Nephrology Resident</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>14/36</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15623,7 +15643,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15670,7 +15690,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15858,7 +15878,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15905,7 +15925,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -15643,7 +15643,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1342,22 +1342,22 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -1424,17 +1424,17 @@
         <v>46</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -1502,22 +1502,22 @@
         <v>47</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>84.7%</t>
         </is>
       </c>
     </row>
@@ -1580,22 +1580,22 @@
         <v>40</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>80.2%</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>76.4%</t>
         </is>
       </c>
     </row>
@@ -1900,22 +1900,22 @@
         <v>40</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>5</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>79.9%</t>
         </is>
       </c>
     </row>
@@ -2529,45 +2529,49 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Sohairhassan</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>30/42</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3438,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3481,7 +3485,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4623,45 +4627,49 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Sohairhassan</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>37/44</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5132,45 +5140,49 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr"/>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Mona Hazaa</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>35/43</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7265,45 +7277,49 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr"/>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Mona Hazaa</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>42/45</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9387,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9512,7 +9528,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9559,12 +9575,12 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>1/50</t>
+          <t>36/50</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -11219,7 +11235,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11360,7 +11376,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11407,12 +11423,12 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>37/47</t>
+          <t>38/47</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
@@ -13204,7 +13220,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13251,7 +13267,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13298,7 +13314,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13435,7 +13451,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13482,7 +13498,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14026,7 +14042,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15056,7 +15072,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15103,7 +15119,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15150,7 +15166,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15287,7 +15303,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15334,7 +15350,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15537,45 +15553,49 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B319" s="5" t="inlineStr">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
         <is>
           <t>B1D2</t>
         </is>
       </c>
-      <c r="C319" s="5" t="inlineStr">
+      <c r="C319" s="2" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D319" s="5" t="inlineStr">
+      <c r="D319" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E319" s="5" t="inlineStr">
+      <c r="E319" s="2" t="inlineStr">
         <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="F319" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G319" s="5" t="inlineStr"/>
-      <c r="H319" s="5" t="inlineStr">
-        <is>
-          <t>0/36</t>
-        </is>
-      </c>
-      <c r="I319" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>Nephrology Resident</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>25/36</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -15894,7 +15914,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -13807,7 +13807,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -14042,7 +14042,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15946,7 +15946,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>78.4%</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
         <v>47</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -1580,22 +1580,22 @@
         <v>40</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -1658,22 +1658,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>74.8%</t>
         </is>
       </c>
     </row>
@@ -1740,22 +1740,22 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -5293,88 +5293,96 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>37/43</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>14/43</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7434,88 +7442,96 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr"/>
-      <c r="H142" s="5" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
-      <c r="I142" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>35/45</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C143" s="5" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E143" s="5" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="inlineStr"/>
-      <c r="H143" s="5" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>12/45</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9751,45 +9767,49 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="inlineStr">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C193" s="5" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D193" s="5" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E193" s="5" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F193" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G193" s="5" t="inlineStr"/>
-      <c r="H193" s="5" t="inlineStr">
-        <is>
-          <t>0/50</t>
-        </is>
-      </c>
-      <c r="I193" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11607,45 +11627,49 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E233" s="5" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G233" s="5" t="inlineStr"/>
-      <c r="H233" s="5" t="inlineStr">
-        <is>
-          <t>0/47</t>
-        </is>
-      </c>
-      <c r="I233" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>39/47</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13690,45 +13714,49 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B278" s="5" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C278" s="5" t="inlineStr">
+      <c r="C278" s="2" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D278" s="5" t="inlineStr">
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E278" s="5" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F278" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G278" s="5" t="inlineStr"/>
-      <c r="H278" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I278" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13930,7 +13930,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16041,7 +16041,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -977,7 +977,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>80.5%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
         <v>40</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
         <v>46</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>83.9%</t>
         </is>
       </c>
     </row>
@@ -1499,22 +1499,22 @@
         <v>47</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>83.2%</t>
         </is>
       </c>
     </row>
@@ -1577,22 +1577,22 @@
         <v>40</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -1655,22 +1655,22 @@
         <v>40</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>72.8%</t>
         </is>
       </c>
     </row>
@@ -1737,17 +1737,17 @@
         <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2581,45 +2581,49 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>B1A1</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>0/42</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Sohairhassan</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>37/42</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3490,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4398,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4445,7 +4449,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4687,45 +4691,49 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>PHYSICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Sohairhassan</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>40/44</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5384,45 +5392,49 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>B1B1</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>0/43</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Mona Hazaa</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>31/43</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7533,45 +7545,49 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>B1B2</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>ENDOCRINOLOGY</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G144" s="5" t="inlineStr"/>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>0/45</t>
-        </is>
-      </c>
-      <c r="I144" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Mona Hazaa</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>40/45</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9811,45 +9827,49 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B194" s="5" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>B1C1</t>
         </is>
       </c>
-      <c r="C194" s="5" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D194" s="5" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E194" s="5" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F194" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G194" s="5" t="inlineStr"/>
-      <c r="H194" s="5" t="inlineStr">
-        <is>
-          <t>0/50</t>
-        </is>
-      </c>
-      <c r="I194" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Melody Ehab</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11671,45 +11691,49 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>B1C2</t>
         </is>
       </c>
-      <c r="C234" s="5" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>GASTROENTEROLOGY</t>
         </is>
       </c>
-      <c r="D234" s="5" t="inlineStr">
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E234" s="5" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G234" s="5" t="inlineStr"/>
-      <c r="H234" s="5" t="inlineStr">
-        <is>
-          <t>0/47</t>
-        </is>
-      </c>
-      <c r="I234" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Melody Ehab</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>37/47</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13512,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -15196,7 +15220,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15380,7 +15404,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -977,7 +977,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1815,17 +1815,17 @@
         <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13782,45 +13782,49 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B279" s="5" t="inlineStr">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>B1D1</t>
         </is>
       </c>
-      <c r="C279" s="5" t="inlineStr">
+      <c r="C279" s="2" t="inlineStr">
         <is>
           <t>NEPHROLOGY</t>
         </is>
       </c>
-      <c r="D279" s="5" t="inlineStr">
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E279" s="5" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="F279" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G279" s="5" t="inlineStr"/>
-      <c r="H279" s="5" t="inlineStr">
-        <is>
-          <t>0/28</t>
-        </is>
-      </c>
-      <c r="I279" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>Nephrology Resident</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14143,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15126,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15173,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15220,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15267,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15404,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15451,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16015,7 +16019,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -977,7 +977,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.1%</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
         <v>46</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -4601,45 +4601,49 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>B1A2</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>NEUROLOGY</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>0/44</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>16/44</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Amir</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Hader Gamal</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Sohairhassan</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -13172,7 +13172,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mona Hazaa</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Yousra</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Nephrology Resident</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Omar Hawary</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Tasneem El-Sayed</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Dr. Melody Ehab</t>
+          <t>Dr. Melody Ehab, Dr. Amir</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Dr. Amir</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Alyaa Sheir, Farah Youssef</t>
+          <t>Farah Youssef, Alyaa Sheir</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Git Department D Bassant</t>
+          <t>Git Department D Bassant, Yousra</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Dr. Amir, Yousra</t>
+          <t>Yousra, Dr. Amir</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Nephrology Resident, Developer</t>
+          <t>Developer, Nephrology Resident</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Farah Youssef</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Farah Youssef, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Farah Youssef</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Yousra, Dr. Amir</t>
+          <t>Dr. Amir, Yousra</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Dr. Amir</t>
+          <t>Dr. Amir, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">

--- a/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_General_&_Special_Internal_2_B1_session_analysis.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dr. Melody Ehab, Dr. Amir</t>
+          <t>Dr. Amir, Dr. Melody Ehab</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Alyaa Sheir</t>
+          <t>Alyaa Sheir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Developer, Nephrology Resident</t>
+          <t>Nephrology Resident, Developer</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>Git Department D Bassant, Yousra</t>
+          <t>Yousra, Git Department D Bassant</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Marina Samir</t>
+          <t>Dr. Marina Samir, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
